--- a/technology_surveys/028_network_and_camera_deployment_survey--technology_surveys.xlsx
+++ b/technology_surveys/028_network_and_camera_deployment_survey--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'single_story',_'label':_'single_story'}</t>
+          <t>single_story</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Single Story', 'label': 'Single Story'}</t>
+          <t>Single Story</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'multi_story',_'label':_'multi_story'}</t>
+          <t>multi_story</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Multi Story', 'label': 'Multi Story'}</t>
+          <t>Multi Story</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'multi_story_-_two_towers',_'label':_'multi_story_-_two_towers'}</t>
+          <t>multi_story_-_two_towers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Multi Story - Two Towers', 'label': 'Multi Story - Two Towers'}</t>
+          <t>Multi Story - Two Towers</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'5,000_sqft',_'label':_'5,000_sqft'}</t>
+          <t>5,000_sqft</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': '5,000 sqft', 'label': '5,000 sqft'}</t>
+          <t>5,000 sqft</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'10,000_sqft',_'label':_'10,000_sqft'}</t>
+          <t>10,000_sqft</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': '10,000 sqft', 'label': '10,000 sqft'}</t>
+          <t>10,000 sqft</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'20,000_sqft',_'label':_'20,000_sqft'}</t>
+          <t>20,000_sqft</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': '20,000 sqft', 'label': '20,000 sqft'}</t>
+          <t>20,000 sqft</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'50,000_sqft',_'label':_'50,000_sqft'}</t>
+          <t>50,000_sqft</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': '50,000 sqft', 'label': '50,000 sqft'}</t>
+          <t>50,000 sqft</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'near_entrances/exits',_'label':_'near_entrances/exits'}</t>
+          <t>near_entrances/exits</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Near Entrances/Exits', 'label': 'Near Entrances/Exits'}</t>
+          <t>Near Entrances/Exits</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'near_security_desks',_'label':_'near_security_desks'}</t>
+          <t>near_security_desks</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Near Security Desks', 'label': 'Near Security Desks'}</t>
+          <t>Near Security Desks</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'near_cameras',_'label':_'near_cameras'}</t>
+          <t>near_cameras</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Near Cameras', 'label': 'Near Cameras'}</t>
+          <t>Near Cameras</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'ptz',_'label':_'ptz'}</t>
+          <t>ptz</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'PTZ', 'label': 'PTZ'}</t>
+          <t>PTZ</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'fixed',_'label':_'fixed'}</t>
+          <t>fixed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Fixed', 'label': 'Fixed'}</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'active',_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Active', 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'not_active',_'label':_'not_active'}</t>
+          <t>not_active</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Not Active', 'label': 'Not Active'}</t>
+          <t>Not Active</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'wireless',_'label':_'wireless'}</t>
+          <t>wireless</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Wireless', 'label': 'Wireless'}</t>
+          <t>Wireless</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'wired',_'label':_'wired'}</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Wired', 'label': 'Wired'}</t>
+          <t>Wired</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'active',_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Active', 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'not_active',_'label':_'not_active'}</t>
+          <t>not_active</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Not Active', 'label': 'Not Active'}</t>
+          <t>Not Active</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'100m',_'label':_'100m'}</t>
+          <t>100m</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': '100M', 'label': '100M'}</t>
+          <t>100M</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'500m',_'label':_'500m'}</t>
+          <t>500m</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': '500M', 'label': '500M'}</t>
+          <t>500M</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'1g',_'label':_'1g'}</t>
+          <t>1g</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': '1G', 'label': '1G'}</t>
+          <t>1G</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'5g',_'label':_'5g'}</t>
+          <t>5g</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': '5G', 'label': '5G'}</t>
+          <t>5G</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'100m',_'label':_'100m'}</t>
+          <t>100m</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': '100M', 'label': '100M'}</t>
+          <t>100M</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'500m',_'label':_'500m'}</t>
+          <t>500m</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': '500M', 'label': '500M'}</t>
+          <t>500M</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'1g',_'label':_'1g'}</t>
+          <t>1g</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': '1G', 'label': '1G'}</t>
+          <t>1G</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'5g',_'label':_'5g'}</t>
+          <t>5g</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': '5G', 'label': '5G'}</t>
+          <t>5G</t>
         </is>
       </c>
     </row>
